--- a/backend/data/Inventaire_Electronique.xlsx
+++ b/backend/data/Inventaire_Electronique.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PRO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Steve\Desktop\Loisirs\API\Atlas-Atelier\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3460D0CC-DACA-403F-AB9E-A73180E291AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549802B2-F35C-487E-A279-13045CD0FC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2803,7 +2803,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3107,9 +3107,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H269"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="24.15234375" customWidth="1"/>
+    <col min="2" max="2" width="29.23046875" customWidth="1"/>
+    <col min="3" max="3" width="29.4609375" customWidth="1"/>
+    <col min="4" max="4" width="28.23046875" customWidth="1"/>
+    <col min="5" max="5" width="17.23046875" customWidth="1"/>
+    <col min="6" max="6" width="56.3828125" customWidth="1"/>
+    <col min="7" max="7" width="39.4609375" customWidth="1"/>
+    <col min="8" max="8" width="20.765625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>894</v>
       </c>
@@ -3135,7 +3145,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -3158,7 +3168,7 @@
         <v>16.739999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -3184,7 +3194,7 @@
         <v>166.65</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -3210,7 +3220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -3236,7 +3246,7 @@
         <v>110.24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -3262,7 +3272,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -3285,7 +3295,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -3308,7 +3318,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -3331,7 +3341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -3357,7 +3367,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -3383,7 +3393,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -3409,7 +3419,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -3435,7 +3445,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -3461,7 +3471,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -3487,7 +3497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -3513,7 +3523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -3536,7 +3546,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -3556,7 +3566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -3582,7 +3592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -3608,7 +3618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -3628,7 +3638,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -3654,7 +3664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -3680,7 +3690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -3706,7 +3716,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -3732,7 +3742,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>0</v>
       </c>
@@ -3758,7 +3768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>0</v>
       </c>
@@ -3781,7 +3791,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -3804,7 +3814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>0</v>
       </c>
@@ -3824,7 +3834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>0</v>
       </c>
@@ -3844,7 +3854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -3864,7 +3874,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>0</v>
       </c>
@@ -3884,7 +3894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>0</v>
       </c>
@@ -3904,7 +3914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -3924,7 +3934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -3944,7 +3954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -3964,7 +3974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>0</v>
       </c>
@@ -3984,7 +3994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -4010,7 +4020,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -4036,7 +4046,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>0</v>
       </c>
@@ -4062,7 +4072,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>0</v>
       </c>
@@ -4088,7 +4098,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -4111,7 +4121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>0</v>
       </c>
@@ -4137,7 +4147,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>0</v>
       </c>
@@ -4163,7 +4173,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>0</v>
       </c>
@@ -4189,7 +4199,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>0</v>
       </c>
@@ -4215,7 +4225,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>0</v>
       </c>
@@ -4241,7 +4251,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>0</v>
       </c>
@@ -4267,7 +4277,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>0</v>
       </c>
@@ -4293,7 +4303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>0</v>
       </c>
@@ -4316,7 +4326,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>0</v>
       </c>
@@ -4342,7 +4352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -4368,7 +4378,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>0</v>
       </c>
@@ -4391,7 +4401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>0</v>
       </c>
@@ -4414,7 +4424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>0</v>
       </c>
@@ -4437,7 +4447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>0</v>
       </c>
@@ -4457,7 +4467,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>0</v>
       </c>
@@ -4477,7 +4487,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>0</v>
       </c>
@@ -4503,7 +4513,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>0</v>
       </c>
@@ -4529,7 +4539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>0</v>
       </c>
@@ -4549,7 +4559,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>0</v>
       </c>
@@ -4569,7 +4579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>0</v>
       </c>
@@ -4592,7 +4602,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>0</v>
       </c>
@@ -4615,7 +4625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>0</v>
       </c>
@@ -4638,7 +4648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -4658,7 +4668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>0</v>
       </c>
@@ -4681,7 +4691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>0</v>
       </c>
@@ -4701,7 +4711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>0</v>
       </c>
@@ -4724,7 +4734,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>0</v>
       </c>
@@ -4744,7 +4754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
         <v>0</v>
       </c>
@@ -4770,7 +4780,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
         <v>0</v>
       </c>
@@ -4793,7 +4803,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
         <v>0</v>
       </c>
@@ -4819,7 +4829,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>0</v>
       </c>
@@ -4845,7 +4855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
         <v>0</v>
       </c>
@@ -4871,7 +4881,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>0</v>
       </c>
@@ -4891,7 +4901,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
         <v>0</v>
       </c>
@@ -4917,7 +4927,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>0</v>
       </c>
@@ -4943,7 +4953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
         <v>0</v>
       </c>
@@ -4969,7 +4979,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -4992,7 +5002,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
         <v>0</v>
       </c>
@@ -5015,7 +5025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>0</v>
       </c>
@@ -5038,7 +5048,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
         <v>0</v>
       </c>
@@ -5064,7 +5074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>0</v>
       </c>
@@ -5084,7 +5094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>0</v>
       </c>
@@ -5110,7 +5120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
         <v>0</v>
       </c>
@@ -5136,7 +5146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
         <v>0</v>
       </c>
@@ -5162,7 +5172,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
         <v>0</v>
       </c>
@@ -5188,7 +5198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
         <v>0</v>
       </c>
@@ -5214,7 +5224,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
         <v>0</v>
       </c>
@@ -5237,7 +5247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
         <v>0</v>
       </c>
@@ -5263,7 +5273,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
         <v>0</v>
       </c>
@@ -5286,7 +5296,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
         <v>0</v>
       </c>
@@ -5312,7 +5322,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
         <v>0</v>
       </c>
@@ -5335,7 +5345,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
         <v>0</v>
       </c>
@@ -5361,7 +5371,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
         <v>0</v>
       </c>
@@ -5387,7 +5397,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
         <v>0</v>
       </c>
@@ -5413,7 +5423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
         <v>0</v>
       </c>
@@ -5439,7 +5449,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
         <v>0</v>
       </c>
@@ -5462,7 +5472,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
         <v>0</v>
       </c>
@@ -5488,7 +5498,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
         <v>0</v>
       </c>
@@ -5514,7 +5524,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
         <v>0</v>
       </c>
@@ -5540,7 +5550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
         <v>0</v>
       </c>
@@ -5563,7 +5573,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
         <v>0</v>
       </c>
@@ -5586,7 +5596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
         <v>0</v>
       </c>
@@ -5606,7 +5616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
         <v>0</v>
       </c>
@@ -5632,7 +5642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
         <v>0</v>
       </c>
@@ -5658,7 +5668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
         <v>0</v>
       </c>
@@ -5684,7 +5694,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
         <v>0</v>
       </c>
@@ -5710,7 +5720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
         <v>0</v>
       </c>
@@ -5733,7 +5743,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
         <v>0</v>
       </c>
@@ -5759,7 +5769,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
         <v>0</v>
       </c>
@@ -5785,7 +5795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
         <v>0</v>
       </c>
@@ -5811,7 +5821,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
         <v>0</v>
       </c>
@@ -5831,7 +5841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
         <v>0</v>
       </c>
@@ -5857,7 +5867,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
         <v>0</v>
       </c>
@@ -5883,7 +5893,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
         <v>0</v>
       </c>
@@ -5906,7 +5916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
         <v>0</v>
       </c>
@@ -5929,7 +5939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
         <v>0</v>
       </c>
@@ -5952,7 +5962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
         <v>0</v>
       </c>
@@ -5978,7 +5988,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
         <v>0</v>
       </c>
@@ -6001,7 +6011,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
         <v>0</v>
       </c>
@@ -6027,7 +6037,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
         <v>0</v>
       </c>
@@ -6053,7 +6063,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
         <v>0</v>
       </c>
@@ -6079,7 +6089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
         <v>0</v>
       </c>
@@ -6102,7 +6112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
         <v>0</v>
       </c>
@@ -6125,7 +6135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
         <v>0</v>
       </c>
@@ -6148,7 +6158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
         <v>0</v>
       </c>
@@ -6171,7 +6181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
         <v>0</v>
       </c>
@@ -6191,7 +6201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
         <v>0</v>
       </c>
@@ -6211,7 +6221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
         <v>0</v>
       </c>
@@ -6231,7 +6241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
         <v>0</v>
       </c>
@@ -6251,7 +6261,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
         <v>0</v>
       </c>
@@ -6271,7 +6281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
         <v>0</v>
       </c>
@@ -6291,7 +6301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
         <v>0</v>
       </c>
@@ -6311,7 +6321,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
         <v>0</v>
       </c>
@@ -6331,7 +6341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
         <v>0</v>
       </c>
@@ -6351,7 +6361,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
         <v>0</v>
       </c>
@@ -6377,7 +6387,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
         <v>0</v>
       </c>
@@ -6397,7 +6407,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
         <v>0</v>
       </c>
@@ -6420,7 +6430,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
         <v>0</v>
       </c>
@@ -6443,7 +6453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
         <v>0</v>
       </c>
@@ -6463,7 +6473,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
         <v>0</v>
       </c>
@@ -6486,7 +6496,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
         <v>0</v>
       </c>
@@ -6512,7 +6522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
         <v>0</v>
       </c>
@@ -6538,7 +6548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
         <v>0</v>
       </c>
@@ -6564,7 +6574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
         <v>0</v>
       </c>
@@ -6584,7 +6594,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
         <v>0</v>
       </c>
@@ -6607,7 +6617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
         <v>0</v>
       </c>
@@ -6630,7 +6640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
         <v>0</v>
       </c>
@@ -6653,7 +6663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
         <v>0</v>
       </c>
@@ -6679,7 +6689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
         <v>0</v>
       </c>
@@ -6699,7 +6709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
         <v>0</v>
       </c>
@@ -6722,7 +6732,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
         <v>0</v>
       </c>
@@ -6745,7 +6755,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
         <v>0</v>
       </c>
@@ -6771,7 +6781,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
         <v>0</v>
       </c>
@@ -6797,7 +6807,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
         <v>0</v>
       </c>
@@ -6823,7 +6833,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
         <v>0</v>
       </c>
@@ -6846,7 +6856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
         <v>0</v>
       </c>
@@ -6872,7 +6882,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
         <v>0</v>
       </c>
@@ -6898,7 +6908,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
         <v>0</v>
       </c>
@@ -6924,7 +6934,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
         <v>0</v>
       </c>
@@ -6950,7 +6960,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
         <v>0</v>
       </c>
@@ -6976,7 +6986,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
         <v>0</v>
       </c>
@@ -7002,7 +7012,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
         <v>0</v>
       </c>
@@ -7028,7 +7038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
         <v>0</v>
       </c>
@@ -7054,7 +7064,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
         <v>0</v>
       </c>
@@ -7080,7 +7090,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
         <v>0</v>
       </c>
@@ -7106,7 +7116,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
         <v>0</v>
       </c>
@@ -7129,7 +7139,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
         <v>0</v>
       </c>
@@ -7155,7 +7165,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
         <v>0</v>
       </c>
@@ -7181,7 +7191,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
         <v>0</v>
       </c>
@@ -7207,7 +7217,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
         <v>0</v>
       </c>
@@ -7227,7 +7237,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
         <v>0</v>
       </c>
@@ -7253,7 +7263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
         <v>0</v>
       </c>
@@ -7279,7 +7289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
         <v>0</v>
       </c>
@@ -7305,7 +7315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
         <v>0</v>
       </c>
@@ -7331,7 +7341,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
         <v>0</v>
       </c>
@@ -7357,7 +7367,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
         <v>0</v>
       </c>
@@ -7383,7 +7393,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
         <v>0</v>
       </c>
@@ -7409,7 +7419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
         <v>0</v>
       </c>
@@ -7429,7 +7439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
         <v>0</v>
       </c>
@@ -7455,7 +7465,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
         <v>0</v>
       </c>
@@ -7481,7 +7491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
         <v>0</v>
       </c>
@@ -7507,7 +7517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
         <v>0</v>
       </c>
@@ -7533,7 +7543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
         <v>0</v>
       </c>
@@ -7559,7 +7569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
         <v>0</v>
       </c>
@@ -7585,7 +7595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
         <v>0</v>
       </c>
@@ -7611,7 +7621,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
         <v>0</v>
       </c>
@@ -7637,7 +7647,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
         <v>0</v>
       </c>
@@ -7663,7 +7673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
         <v>0</v>
       </c>
@@ -7689,7 +7699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
         <v>0</v>
       </c>
@@ -7715,7 +7725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
         <v>0</v>
       </c>
@@ -7741,7 +7751,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
         <v>0</v>
       </c>
@@ -7767,7 +7777,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
         <v>0</v>
       </c>
@@ -7793,7 +7803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
         <v>0</v>
       </c>
@@ -7819,7 +7829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
         <v>0</v>
       </c>
@@ -7845,7 +7855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B197" t="s">
         <v>190</v>
       </c>
@@ -7865,7 +7875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
         <v>0</v>
       </c>
@@ -7888,7 +7898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
         <v>0</v>
       </c>
@@ -7914,7 +7924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
         <v>0</v>
       </c>
@@ -7937,7 +7947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
         <v>0</v>
       </c>
@@ -7960,7 +7970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
         <v>0</v>
       </c>
@@ -7983,7 +7993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
         <v>0</v>
       </c>
@@ -8009,7 +8019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
         <v>0</v>
       </c>
@@ -8032,7 +8042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
         <v>0</v>
       </c>
@@ -8058,7 +8068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
         <v>0</v>
       </c>
@@ -8084,7 +8094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
         <v>0</v>
       </c>
@@ -8107,7 +8117,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
         <v>0</v>
       </c>
@@ -8133,7 +8143,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
         <v>0</v>
       </c>
@@ -8156,7 +8166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
         <v>0</v>
       </c>
@@ -8182,7 +8192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
         <v>0</v>
       </c>
@@ -8208,7 +8218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
         <v>0</v>
       </c>
@@ -8234,7 +8244,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
         <v>0</v>
       </c>
@@ -8260,7 +8270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
         <v>0</v>
       </c>
@@ -8286,7 +8296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
         <v>0</v>
       </c>
@@ -8309,7 +8319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
         <v>0</v>
       </c>
@@ -8335,7 +8345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
         <v>0</v>
       </c>
@@ -8361,7 +8371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
         <v>0</v>
       </c>
@@ -8387,7 +8397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
         <v>0</v>
       </c>
@@ -8413,7 +8423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
         <v>0</v>
       </c>
@@ -8439,7 +8449,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
         <v>0</v>
       </c>
@@ -8465,7 +8475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
         <v>0</v>
       </c>
@@ -8491,7 +8501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
         <v>0</v>
       </c>
@@ -8517,7 +8527,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B224" t="s">
         <v>214</v>
       </c>
@@ -8540,7 +8550,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B225" t="s">
         <v>214</v>
       </c>
@@ -8563,7 +8573,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
         <v>0</v>
       </c>
@@ -8589,7 +8599,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
         <v>0</v>
       </c>
@@ -8615,7 +8625,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
         <v>0</v>
       </c>
@@ -8641,7 +8651,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
         <v>0</v>
       </c>
@@ -8667,7 +8677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
         <v>0</v>
       </c>
@@ -8693,7 +8703,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
         <v>0</v>
       </c>
@@ -8719,7 +8729,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
         <v>0</v>
       </c>
@@ -8745,7 +8755,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
         <v>0</v>
       </c>
@@ -8771,7 +8781,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
         <v>0</v>
       </c>
@@ -8797,7 +8807,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
         <v>0</v>
       </c>
@@ -8817,7 +8827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
         <v>0</v>
       </c>
@@ -8843,7 +8853,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
         <v>0</v>
       </c>
@@ -8869,7 +8879,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
         <v>0</v>
       </c>
@@ -8895,7 +8905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
         <v>0</v>
       </c>
@@ -8921,7 +8931,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
         <v>0</v>
       </c>
@@ -8947,7 +8957,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
         <v>0</v>
       </c>
@@ -8973,7 +8983,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
         <v>0</v>
       </c>
@@ -8999,7 +9009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
         <v>0</v>
       </c>
@@ -9025,7 +9035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
         <v>0</v>
       </c>
@@ -9045,7 +9055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
         <v>0</v>
       </c>
@@ -9071,7 +9081,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
         <v>0</v>
       </c>
@@ -9097,7 +9107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
         <v>0</v>
       </c>
@@ -9123,7 +9133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
         <v>0</v>
       </c>
@@ -9149,7 +9159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
         <v>0</v>
       </c>
@@ -9175,7 +9185,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A250" t="s">
         <v>0</v>
       </c>
@@ -9201,7 +9211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
         <v>0</v>
       </c>
@@ -9227,7 +9237,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
         <v>0</v>
       </c>
@@ -9247,7 +9257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
         <v>0</v>
       </c>
@@ -9273,7 +9283,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
         <v>0</v>
       </c>
@@ -9287,7 +9297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
         <v>0</v>
       </c>
@@ -9301,7 +9311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
         <v>0</v>
       </c>
@@ -9315,7 +9325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
         <v>0</v>
       </c>
@@ -9329,7 +9339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A258" t="s">
         <v>0</v>
       </c>
@@ -9343,7 +9353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
         <v>0</v>
       </c>
@@ -9357,7 +9367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
         <v>0</v>
       </c>
@@ -9371,7 +9381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
         <v>0</v>
       </c>
@@ -9385,7 +9395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A262" t="s">
         <v>0</v>
       </c>
@@ -9399,7 +9409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
         <v>0</v>
       </c>
@@ -9413,7 +9423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
         <v>0</v>
       </c>
@@ -9427,7 +9437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
         <v>0</v>
       </c>
@@ -9441,7 +9451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
         <v>0</v>
       </c>
@@ -9455,7 +9465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
         <v>0</v>
       </c>
@@ -9469,7 +9479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
         <v>0</v>
       </c>
@@ -9483,7 +9493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A269" t="s">
         <v>0</v>
       </c>
